--- a/hall/resources/sample/SeasonTier.xlsx
+++ b/hall/resources/sample/SeasonTier.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>序列ID</t>
   </si>
@@ -86,6 +86,9 @@
     <t>段位类型</t>
   </si>
   <si>
+    <t>赛季结算可获得的徽章</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>ranktype</t>
+  </si>
+  <si>
+    <t>SeasonBadge</t>
   </si>
   <si>
     <t>青铜三</t>
@@ -1449,18 +1455,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="4" max="4" width="14.125" customWidth="1"/>
     <col min="5" max="5" width="19.625" customWidth="1"/>
     <col min="6" max="6" width="14.875" customWidth="1"/>
-    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
     <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1485,56 +1492,65 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1544,7 +1560,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1552,23 +1568,26 @@
         <v>4059195</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>1140001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1576,23 +1595,26 @@
         <v>4059196</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>1140001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1600,23 +1622,26 @@
         <v>4059197</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>1140001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1624,25 +1649,28 @@
         <v>4059198</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>1140002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1650,23 +1678,26 @@
         <v>4059199</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>1140002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1674,23 +1705,26 @@
         <v>4059200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>1140002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1698,25 +1732,28 @@
         <v>4059201</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11">
+        <v>1140003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1724,23 +1761,26 @@
         <v>4059202</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12">
+        <v>1140003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1748,23 +1788,26 @@
         <v>4059203</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13">
+        <v>1140003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1772,25 +1815,28 @@
         <v>4059204</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14">
+        <v>1140004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1798,23 +1844,26 @@
         <v>4059205</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15">
+        <v>1140004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1822,23 +1871,26 @@
         <v>4059206</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16">
+        <v>1140004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1846,25 +1898,28 @@
         <v>4059207</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>1140005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1872,23 +1927,26 @@
         <v>4059208</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18">
+        <v>1140005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1896,23 +1954,26 @@
         <v>4059209</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>1140005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1920,25 +1981,28 @@
         <v>4059210</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20">
+        <v>1140006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1946,25 +2010,28 @@
         <v>4059211</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21">
+        <v>1140006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1972,25 +2039,28 @@
         <v>4059212</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H22" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22">
+        <v>1140006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1998,25 +2068,28 @@
         <v>4059213</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23">
+        <v>1140006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2024,25 +2097,28 @@
         <v>4059214</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24">
+        <v>1140006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2050,25 +2126,28 @@
         <v>4059096</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25">
+        <v>1140001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2076,25 +2155,28 @@
         <v>4059097</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26">
+        <v>1140002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2102,25 +2184,28 @@
         <v>4059098</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27">
+        <v>1140003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2128,22 +2213,25 @@
         <v>4059099</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1140004</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonTier.xlsx
+++ b/hall/resources/sample/SeasonTier.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
   <si>
     <t>序列ID</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>200_499</t>
+  </si>
+  <si>
+    <t>1960000_100</t>
   </si>
   <si>
     <t>青铜一</t>
@@ -459,12 +462,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1600,7 +1603,9 @@
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
@@ -1622,12 +1627,14 @@
         <v>4059197</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1"/>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
@@ -1649,13 +1656,13 @@
         <v>4059198</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
@@ -1678,12 +1685,14 @@
         <v>4059199</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1"/>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
@@ -1705,12 +1714,14 @@
         <v>4059200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
@@ -1732,13 +1743,13 @@
         <v>4059201</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
@@ -1761,12 +1772,14 @@
         <v>4059202</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="1"/>
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
@@ -1788,12 +1801,14 @@
         <v>4059203</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
@@ -1815,13 +1830,13 @@
         <v>4059204</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="b">
         <v>0</v>
@@ -1844,12 +1859,14 @@
         <v>4059205</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="1"/>
       <c r="F15" s="1" t="b">
         <v>0</v>
       </c>
@@ -1871,12 +1888,14 @@
         <v>4059206</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F16" s="1" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1917,10 @@
         <v>4059207</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>23</v>
@@ -1927,12 +1946,14 @@
         <v>4059208</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F18" s="1" t="b">
         <v>0</v>
       </c>
@@ -1954,12 +1975,14 @@
         <v>4059209</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F19" s="1" t="b">
         <v>0</v>
       </c>
@@ -1981,13 +2004,13 @@
         <v>4059210</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="b">
         <v>0</v>
@@ -2010,13 +2033,13 @@
         <v>4059211</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="1" t="b">
         <v>0</v>
@@ -2039,13 +2062,13 @@
         <v>4059212</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="b">
         <v>0</v>
@@ -2068,13 +2091,13 @@
         <v>4059213</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" s="1" t="b">
         <v>0</v>
@@ -2097,13 +2120,13 @@
         <v>4059214</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24" s="1" t="b">
         <v>0</v>
@@ -2126,10 +2149,10 @@
         <v>4059096</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -2155,10 +2178,10 @@
         <v>4059097</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>23</v>
@@ -2184,10 +2207,10 @@
         <v>4059098</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>23</v>
@@ -2213,10 +2236,10 @@
         <v>4059099</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>23</v>
